--- a/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NHYDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="92">
   <si>
     <t>NHYDY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>4144800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4960800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6146300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4263500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4367500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3452900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3250600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3169900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1249900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2787400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2567200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3202000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3928000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4515500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4529900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4254800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4330700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4220300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4336500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4493100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2639900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2847400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2839100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2620100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>2713700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3246800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3512800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2667000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2333100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2229300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1995300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1897500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>625800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1676100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1603700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1894400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2471300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2899500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2997100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2845600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2839000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2625700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2710500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2733500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2826500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1710000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1835000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1827600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1651100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1588800</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>1431100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1714000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2633500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1596500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2034400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1223600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1255300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1272400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>624100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1111300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>963600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1307600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1456800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1616100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1532800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1409100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1491700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1442300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1509700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1666600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>929900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1012400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1011600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>969000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>898600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,48 +1543,48 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>27000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>27700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>185300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>100900</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1580,11 +1600,11 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1645,86 +1668,89 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3">
         <v>213500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>202000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>205600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>184700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>199100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>196400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>177300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>174000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>88100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>173300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>184400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>192100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>236000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>269100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>243400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>237500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>193900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>189400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>193400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>207100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>228100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>167900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>160800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>166700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>197200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>174600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>4012700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4235300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4683700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3694400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3418800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3214700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2965200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2948300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>535800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2595600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2728100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2976300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3972200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4488800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4454100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4252500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4310600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3857600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3914800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3978300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3970800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2370900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2506300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2542000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2378000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2317800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>132100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>725500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1462600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>569100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>948700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>238300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>285400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>221500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>714100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>191800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-160900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>225700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-44200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>26700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>75900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>20100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>210400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>305500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>358100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>522300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>269000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>341100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>297200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>242200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>169700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>54100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>72400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-96300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>221000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>83700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-62000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>54000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>65600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>184400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-152000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>62700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-426500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>52700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-170700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-51800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>20800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-51000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-27200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-30000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-77500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>60900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-102800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>27100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>44600</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>426600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1004500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1571900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>974800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1259200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>374000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>517300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>473200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1085900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>220600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>271500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>345500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>125200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>267600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>260600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>163000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>372600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>468800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>527000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>673000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>497900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>399100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>491000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>435600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>388800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,86 +2380,89 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>28600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>28000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>26400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>27000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>30300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>16100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>13300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>12400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>4700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>8200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>10400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>13400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>157600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>772400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1338300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>769700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1009300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>152400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>318800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>263600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>872200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-121600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-222900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-169300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-61300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>167200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>260400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>306600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>432500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>325100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>230100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>313900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>224900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>208700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>142800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>140800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>281800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>183400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>207400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>46500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>93300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>77000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>84700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>24500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>29100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-46300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>55000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>17000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>72600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>48400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>81300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>15600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>72300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>49100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>87200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>100500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>14800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>631600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1056500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>586400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>801900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>105900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>225500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>186600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>787500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-150600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-176600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-73500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-167400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-22100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-14000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-84700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>94500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>212000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>225300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>416800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>252900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>181000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>226700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>124400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>23600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>648000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1069700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>524900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>669900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>96700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>204900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>180700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>761500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-128000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-154900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-52700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-151500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-78200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>76800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>215600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>226900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>405100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>235900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>171800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>217300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>130700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3194,12 +3255,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>3400</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -3207,37 +3268,37 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>38300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-37700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-230600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>1600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-28600</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-54100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-72400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>96300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-221000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-83700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>62000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-54000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-65600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-184400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>152000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-62700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>426500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-52700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>170700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>51800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>51000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>27200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>38200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>77500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-60900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>102800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>3800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>27000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>648000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1069700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>524900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>670300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>94900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>243100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>143000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>531000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-22600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-126400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-183500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-52700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-151500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-78200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>76800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>215600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>226900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>405100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>235900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>171800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>217300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>130700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>27000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>648000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1069700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>524900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>670300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>94900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>243100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>143000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>531000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-22600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-126400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-183500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-52700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-151500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-78200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>76800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>215600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>226900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>405100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>235900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>171800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>217300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>130700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,297 +4305,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1550100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1155200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1595600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1472100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1859300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1324600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1792500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1772300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1811800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2427700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1791500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2094600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2951600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2802900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2445300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2324700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1935400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1767600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1895000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1411900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1489200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1826900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1772200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1558500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1231800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1359800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1273500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1224500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>690500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>676400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>700300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>581300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1016700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1369600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2067200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>925500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1027500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>991000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>980500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>388400</v>
+      </c>
+      <c r="E42" s="3">
         <v>966500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>792500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>814200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>301600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>279800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>138700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>373000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>352800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>458700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>165300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>197000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>108000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>257700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>498400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>699800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>799200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1217100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>740600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>401300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>439800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>463900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>472400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>602900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>587200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>279600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>177500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>196100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>180500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>183700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>200400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>195800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>216300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>200600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>244200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>259400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>600500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>580000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>624900</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>572400</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3135700</v>
+      </c>
+      <c r="E43" s="3">
         <v>3222400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2572600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2796700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2788000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2960500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2509500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2735900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2692200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2674800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2505200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2474300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2571100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2710400</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4535,225 +4628,231 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
         <v>2053100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1916200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2485800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2098400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2769100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2681000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2665200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2340300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2222700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2398100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2471900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2313800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1559100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1584500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1342000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1417300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3052800</v>
+      </c>
+      <c r="E44" s="3">
         <v>2845400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2757500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2723100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2626600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2595900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2481100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2481200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2365500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2335200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2509700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2592500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2687500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2888800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2824500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2969600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2790300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2308200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1783900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1547700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1346600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1420300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2019000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1953900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2064700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2275600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2303900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2609300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2626900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2830700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2987800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2446600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2285100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2237700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2398100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1573000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1498300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1548300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1526600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1420000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>197400</v>
+      </c>
+      <c r="E45" s="3">
         <v>170000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>364500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>115200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>147000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>122500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>202700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>122300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>89300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>506100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>645900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>161800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>253900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>124600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4778,24 +4877,24 @@
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4811,8 +4910,8 @@
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK45" s="3">
-        <v>0</v>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL45" s="3">
         <v>0</v>
@@ -4820,505 +4919,520 @@
       <c r="AM45" s="3">
         <v>0</v>
       </c>
-      <c r="AN45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO45" s="3">
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP45" s="3">
         <v>100</v>
       </c>
-      <c r="AP45" s="3" t="s">
+      <c r="AQ45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8324300</v>
+      </c>
+      <c r="E46" s="3">
         <v>8359600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8082800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7921200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7722400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7759500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6656600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7504900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7272100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7786500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8253900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7217200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7715200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8933000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8381600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8805000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8680700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7834500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6161000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5709900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4778100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5039700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6220500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6382300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6126600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6272800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5939600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6848100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6712900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6370100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6204900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5565400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5480700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5926900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6325700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5422900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4583400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4740300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4484500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4390100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2201300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2223400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2330900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2309300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2269100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2252000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2348000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2303200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2333900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2078600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2196300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2309800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2264800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2157400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1995700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2139000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1902400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1669800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1661200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1639100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1620400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1709100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1790700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1220500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1278300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1402500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1272900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1421300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1264500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1284800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1305300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1134900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1139600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1144700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1299300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2104800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2176900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2458200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2442200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2383800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7953000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7897700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7750700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7655600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7516500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7156500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6860100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7159600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6986200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7140500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7394300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6973400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6808700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6484500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5892200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5899500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5589200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5176500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5139600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5300600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5068900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5346400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6654500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6955000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7139400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7892200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8217200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8909600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8463300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8251000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8390300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6777500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6821700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7588300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8444900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6542100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>6670700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7352000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7241900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>6716900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>737900</v>
+      </c>
+      <c r="E49" s="3">
         <v>748900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>759700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>772500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>780100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>753800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>742500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>791400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>785000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>807100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>833000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1014900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>953000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>940600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>872700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>927900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>889200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>821900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>832600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>862900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>827400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>872700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>969200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1003200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1039500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1281300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1272900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1407600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1328000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1260400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1291000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1094100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1192800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1316300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1471900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>628400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>645800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>729800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>716500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>674300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1948800</v>
+      </c>
+      <c r="E52" s="3">
         <v>2017400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1442000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1912400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1807500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1855000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1272400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1875600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1880000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1866500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1380800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1731900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1709700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1694600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1535900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1792600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1727800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2033600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1719200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1577300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2964500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3126800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1394500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1241200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1246600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1307400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1493200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1516400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1538900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1473100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1415700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1311300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1237900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1249900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1550800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1229500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1189000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1275900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1241600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21165400</v>
+      </c>
+      <c r="E54" s="3">
         <v>21247000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20662900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20571000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20095600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19776800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18253100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19634700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19257200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19679200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20360500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19247100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19451400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20210100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18678000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19564000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18789300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17536300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15513700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15089800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15259200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16094600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17029400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16802100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16830500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18156200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18195900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20103100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19307700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18639300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18607200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15883200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15872800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>17226200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15927700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>15265800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>16556200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>16126800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>15372100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2708700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2655700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1892800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2507000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2523000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2560900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1733100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2481500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2471400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2450600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1842200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2331100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2381600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2457200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2292100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2525800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2765700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2298400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1901800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1909600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1642500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1732400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1962600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1809700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1691000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2183800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2068800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2373000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2429800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2507100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2299400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2036400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2184200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2237200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2266100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1198100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1212600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1260600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1246300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1125900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>675000</v>
+      </c>
+      <c r="E58" s="3">
         <v>523900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>808400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>829100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>762100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1250000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1021100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1323400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1524800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>754300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>701300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>540500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>491700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>564000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>634400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1048500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>739500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>646800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>393700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>393500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>442200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>466400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>491800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>700500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>718600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>782800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>681500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>731100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>945500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1009000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1057500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>675900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>508300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>571600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>954700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1049600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>433200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>429200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>404800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>439200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>984700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1330800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>975300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>809900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>734600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>892200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>701400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>899800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>803500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>755900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>775900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1040300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>894900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1026900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1099000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1102300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1017300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1146500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>663900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>488300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>379600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>400400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>554400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>370700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>376900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>483300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>535900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>492900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>426400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>529000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>684000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>603300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>509000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>526400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1202600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>410100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>337100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>411300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>458100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>516900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4368300</v>
+      </c>
+      <c r="E60" s="3">
         <v>4510400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4676500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4146000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4019700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4703100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4349200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4704600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4799600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3960800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4342400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3911900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3768200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4048000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4025600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4676600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4522500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4091700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2959400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2791300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2464300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2599200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3008800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2880900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2786600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3450000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3286200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3597000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3801800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4045200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4040900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3315500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3201600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3335200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3860100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2657800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1982800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2101200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2081900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2931600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2941900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2819700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2875400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2949500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2283400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2037400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2266300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2145800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2862000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2857700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2807800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2775900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2831300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2447800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1966500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1997200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1927300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2398100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2310300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2225300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2347100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2569900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2620900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2694100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2156700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2087200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2405400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2153000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1195400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1054000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>806700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>959300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>948900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1043500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>356300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>368600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>415900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>550400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>420300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1126400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1098600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1119900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1177200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1142000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1088100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1127800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1304200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1225400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1231800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1165300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1052300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1113000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1063200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2067400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2223100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2306000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2416100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2541500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2318000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3260900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3439400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3429000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3510900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3361000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3719000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3516400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3912800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3455400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3278400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3547300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2811300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2795200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3056100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3561200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2735700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2775600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2844800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2661200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2833800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9882300</v>
+      </c>
+      <c r="E66" s="3">
         <v>9952000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10039100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9652600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9558300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9394400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8795000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9615900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9512700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9361100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9790500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9143700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9017800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9277000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9043200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9430600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9365200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8947600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8220700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7761700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8228700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8679200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9335600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9322800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9168900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9726700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9348900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10441200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9925000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9051500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8925000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7391100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7415000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7870700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>8828100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6353700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5731300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6081600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6027600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6016400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6455300</v>
+      </c>
+      <c r="E72" s="3">
         <v>6586700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5943400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6235200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5939300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6126400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5259200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5487000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5347600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5727400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6003500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5895800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5914400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6830300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6616700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6613600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6265000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6022700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4972300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4877400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5029300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5304700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5389100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5010800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5033300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5159600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5837800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6405600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6299500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6466900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6443600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5915000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5838300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6351300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6534600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6130800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5895000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6408300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>6190900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>6060300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10478700</v>
+      </c>
+      <c r="E76" s="3">
         <v>10525400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9904400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10178200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9811900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9735200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8930700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9413300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9238400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9741300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9918700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9664100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9970100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10380800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9634900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10133300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9424100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8588600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7292900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7328000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7030500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7415500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7693800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7479300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7661600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8429500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8847000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9661900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9382700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9587900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9682200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8492100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8457800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9355400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>10077300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>9574000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>9534500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>10474600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>10099100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>9355600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>27000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>648000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1069700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>524900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>670300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>94900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>243100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>143000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>531000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-22600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-126400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-183500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-52700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-151500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-78200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>76800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>215600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>226900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>405100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>235900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>171800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>217300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>130700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>133800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>248800</v>
+      </c>
+      <c r="E83" s="3">
         <v>242000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>187500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>232800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>234400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>228200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>199600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>218200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>218300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>209300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>196700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>219400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>230700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>240400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>206700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>205700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>184700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>226800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>197700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>178000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>186100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>415700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>211200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>400700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>222800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>337000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>269100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>243500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>237500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>193900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>189400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>193300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>207100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>228100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>168000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>160800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>166700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>197300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>911700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-194200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>792900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>370200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>755200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>378300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>581200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>442100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>392100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>327200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>477100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>943200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>354100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>790800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>569100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1432200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>791900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>615000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-54000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>563900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>457800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>221800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>138000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>628700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>420200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>300600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>88200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>106500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>263300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>155300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>215800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>740900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>341600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>501400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>82400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>523700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>284800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-259600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-282600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-402700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-216400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-262700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-257000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-384700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-272300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-304000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-284200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-426900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-324300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-251700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3690000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2542000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2063000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2334000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1369000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-182900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-127700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-116400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-320200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-237200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-258000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-184600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-284000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-183700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-157200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-148500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-353000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-173800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-156300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-172100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-315900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-97600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-545200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-695800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-268700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-260600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-374000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-313900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>27300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-522000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-528600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-706400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-443400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-297600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-398200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-393500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-45700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-154100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-265300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-138800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>85700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-128800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>12700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-131700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-456900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-194500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-324000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-234000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-310700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-182800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-292200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-154800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-159600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1571400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>220100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-244300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-331100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,80 +10455,81 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>607500</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>13500</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>439400</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>470600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>1072900</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-11200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-281500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1051400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-24300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-241200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-272200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10303,49 +10537,52 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-295800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-366300</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-8700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-303900</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-14300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-564500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-192700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-113600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-85000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-528300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>343600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-569600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-135100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-445800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>838600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-42400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1340300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-118000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1146000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-13800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-151900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>38200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-250200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-49300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-493200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-73900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>669000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-107400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-208300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>531200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>115200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>45700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>22200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-344300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-292100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>101800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>602000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-283600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>26000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-212400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-22300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-91100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>25600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-28700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>60200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-75000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-42300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>55000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>82400</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>67800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>82100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>29800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-42800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>69600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>76900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>23900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>13900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-19000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>32500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-33400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-95400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>58500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>21100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>44000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-30700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>31000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>9000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>30300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-21500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>414300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-496300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>137100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-411100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>370300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-336800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-55200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-461000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>562200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-313900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-785500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>102100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>371700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>127200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>317400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-161200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>388600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-127500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>483000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-260500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>213700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>326700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>188700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>519300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>11800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-96000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>119100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-377400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-266600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-697600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1141700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-39400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>36500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>10500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-156300</v>
       </c>
     </row>
